--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -11104,7 +11104,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="A36:E36"/>
@@ -11116,6 +11115,7 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="A42:E42"/>
@@ -11134,7 +11134,7 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -11104,6 +11104,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="A36:E36"/>
@@ -11115,7 +11116,6 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="A42:E42"/>
@@ -11134,7 +11134,7 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -9943,464 +9943,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -10019,7 +10019,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10215,7 +10215,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10306,7 +10306,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10339,7 +10339,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -10617,7 +10617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="42" customWidth="1" style="1223" min="1" max="1"/>
@@ -10717,414 +10717,463 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="1223">
+    <row r="8">
       <c r="A8" s="597" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN DEL PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B9" s="100" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>No de Contrato</t>
+        </is>
+      </c>
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="D10" s="100" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>Contratista</t>
+        </is>
+      </c>
+      <c r="B11" s="100" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="B12" s="100" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1223">
+      <c r="A13" s="597" t="inlineStr">
         <is>
           <t>DATOS GENERALES DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="1223">
-      <c r="A9" s="99" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="1223">
+      <c r="A14" s="99" t="inlineStr">
         <is>
           <t>Número de pisos (torre)</t>
         </is>
       </c>
-      <c r="B9" s="100" t="n"/>
-      <c r="C9" s="593" t="inlineStr">
+      <c r="B14" s="100" t="n"/>
+      <c r="C14" s="593" t="inlineStr">
         <is>
           <t>pisos</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="1223">
-      <c r="A10" s="101" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="1223">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>Número de sótanos (parqueaderos)</t>
         </is>
       </c>
-      <c r="B10" s="102" t="n"/>
-      <c r="C10" s="590" t="inlineStr">
+      <c r="B15" s="102" t="n"/>
+      <c r="C15" s="590" t="inlineStr">
         <is>
           <t>niveles</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="1223">
-      <c r="A11" s="99" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="1223">
+      <c r="A16" s="99" t="inlineStr">
         <is>
           <t>Área del lote</t>
         </is>
       </c>
-      <c r="B11" s="100" t="n"/>
-      <c r="C11" s="593" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="1223">
-      <c r="A12" s="101" t="inlineStr">
-        <is>
-          <t>Área construida típica por piso</t>
-        </is>
-      </c>
-      <c r="B12" s="102" t="n"/>
-      <c r="C12" s="590" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="1223">
-      <c r="A13" s="99" t="inlineStr">
-        <is>
-          <t>Área construida - torre (12 pisos)</t>
-        </is>
-      </c>
-      <c r="B13" s="103">
-        <f>B9*B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="593" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="1223">
-      <c r="A14" s="101" t="inlineStr">
-        <is>
-          <t>Área construida - sótanos (2 niveles)</t>
-        </is>
-      </c>
-      <c r="B14" s="102" t="n"/>
-      <c r="C14" s="590" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="1223">
-      <c r="A15" s="99" t="inlineStr">
-        <is>
-          <t>Área cubierta / cuarto de máquinas / tanques</t>
-        </is>
-      </c>
-      <c r="B15" s="100" t="n"/>
-      <c r="C15" s="593" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="1223">
-      <c r="A16" s="101" t="inlineStr">
-        <is>
-          <t>ÁREA TOTAL CONSTRUIDA</t>
-        </is>
-      </c>
-      <c r="B16" s="104">
-        <f>B13+B14+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="590" t="inlineStr">
+      <c r="B16" s="100" t="n"/>
+      <c r="C16" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="1223">
-      <c r="A17" s="99" t="inlineStr">
+      <c r="A17" s="101" t="inlineStr">
         <is>
-          <t>Número de apartamentos</t>
+          <t>Área construida típica por piso</t>
         </is>
       </c>
-      <c r="B17" s="100" t="n"/>
-      <c r="C17" s="593" t="inlineStr">
+      <c r="B17" s="102" t="n"/>
+      <c r="C17" s="590" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="1223">
-      <c r="A18" s="101" t="inlineStr">
+      <c r="A18" s="99" t="inlineStr">
         <is>
-          <t>Área promedio por apartamento (vendible)</t>
+          <t>Área construida - torre (12 pisos)</t>
         </is>
       </c>
-      <c r="B18" s="102" t="n"/>
-      <c r="C18" s="590" t="inlineStr">
+      <c r="B18" s="103">
+        <f>B14*B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="1223">
-      <c r="A19" s="99" t="inlineStr">
+      <c r="A19" s="101" t="inlineStr">
         <is>
-          <t>Número de parqueaderos</t>
+          <t>Área construida - sótanos (2 niveles)</t>
         </is>
       </c>
-      <c r="B19" s="100" t="n"/>
-      <c r="C19" s="593" t="inlineStr">
+      <c r="B19" s="102" t="n"/>
+      <c r="C19" s="590" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="1223">
+      <c r="A20" s="99" t="inlineStr">
+        <is>
+          <t>Área cubierta / cuarto de máquinas / tanques</t>
+        </is>
+      </c>
+      <c r="B20" s="100" t="n"/>
+      <c r="C20" s="593" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="1223">
+      <c r="A21" s="101" t="inlineStr">
+        <is>
+          <t>ÁREA TOTAL CONSTRUIDA</t>
+        </is>
+      </c>
+      <c r="B21" s="104">
+        <f>B18+B19+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="590" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="1223">
+      <c r="A22" s="99" t="inlineStr">
+        <is>
+          <t>Número de apartamentos</t>
+        </is>
+      </c>
+      <c r="B22" s="100" t="n"/>
+      <c r="C22" s="593" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="1223">
-      <c r="A20" s="101" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="1223">
+      <c r="A23" s="101" t="inlineStr">
         <is>
-          <t>Número de ascensores</t>
+          <t>Área promedio por apartamento (vendible)</t>
         </is>
       </c>
-      <c r="B20" s="102" t="n"/>
-      <c r="C20" s="590" t="inlineStr">
+      <c r="B23" s="102" t="n"/>
+      <c r="C23" s="590" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="1223">
-      <c r="A21" s="99" t="inlineStr">
-        <is>
-          <t>Altura total aproximada (sótano a cubierta)</t>
-        </is>
-      </c>
-      <c r="B21" s="100" t="n"/>
-      <c r="C21" s="593" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="592" t="n"/>
-      <c r="B22" s="592" t="n"/>
-      <c r="C22" s="592" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="1223">
-      <c r="A23" s="594" t="inlineStr">
-        <is>
-          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
+          <t>m²</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="1223">
       <c r="A24" s="99" t="inlineStr">
         <is>
-          <t>Administración (A)</t>
+          <t>Número de parqueaderos</t>
         </is>
       </c>
-      <c r="B24" s="466" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="B24" s="100" t="n"/>
       <c r="C24" s="593" t="inlineStr">
         <is>
-          <t>% s/costo directo</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="1223">
       <c r="A25" s="101" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
+          <t>Número de ascensores</t>
         </is>
       </c>
-      <c r="B25" s="467" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="B25" s="102" t="n"/>
       <c r="C25" s="590" t="inlineStr">
         <is>
-          <t>% s/costo directo</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="1223">
       <c r="A26" s="99" t="inlineStr">
         <is>
-          <t>Utilidad (U)</t>
+          <t>Altura total aproximada (sótano a cubierta)</t>
         </is>
       </c>
-      <c r="B26" s="466" t="n">
-        <v>0.12</v>
+      <c r="B26" s="100" t="n"/>
+      <c r="C26" s="593" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
       </c>
-      <c r="C26" s="593" t="inlineStr">
+    </row>
+    <row r="27">
+      <c r="A27" s="592" t="n"/>
+      <c r="B27" s="592" t="n"/>
+      <c r="C27" s="592" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="1223">
+      <c r="A28" s="594" t="inlineStr">
+        <is>
+          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="1223">
+      <c r="A29" s="99" t="inlineStr">
+        <is>
+          <t>Administración (A)</t>
+        </is>
+      </c>
+      <c r="B29" s="466" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C29" s="593" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="1223">
-      <c r="A27" s="101" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="1223">
+      <c r="A30" s="101" t="inlineStr">
+        <is>
+          <t>Imprevistos (I)</t>
+        </is>
+      </c>
+      <c r="B30" s="467" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C30" s="590" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="1223">
+      <c r="A31" s="99" t="inlineStr">
+        <is>
+          <t>Utilidad (U)</t>
+        </is>
+      </c>
+      <c r="B31" s="466" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C31" s="593" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="1223">
+      <c r="A32" s="101" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="B27" s="467" t="n">
+      <c r="B32" s="467" t="n">
         <v>0.19</v>
       </c>
-      <c r="C27" s="590" t="inlineStr">
+      <c r="C32" s="590" t="inlineStr">
         <is>
           <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="592" t="n"/>
-      <c r="B28" s="592" t="n"/>
-      <c r="C28" s="592" t="n"/>
+    <row r="33">
+      <c r="A33" s="592" t="n"/>
+      <c r="B33" s="592" t="n"/>
+      <c r="C33" s="592" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="1223">
-      <c r="A29" s="105" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="1223">
+      <c r="A34" s="105" t="inlineStr">
         <is>
           <t>AIU TOTAL (A+I+U)</t>
         </is>
       </c>
-      <c r="B29" s="468">
-        <f>B24+B25+B26</f>
+      <c r="B34" s="468">
+        <f>B29+B30+B31</f>
         <v/>
       </c>
-      <c r="C29" s="592" t="n"/>
+      <c r="C34" s="592" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="592" t="n"/>
-      <c r="B30" s="592" t="n"/>
-      <c r="C30" s="592" t="n"/>
+    <row r="35">
+      <c r="A35" s="592" t="n"/>
+      <c r="B35" s="592" t="n"/>
+      <c r="C35" s="592" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="1223">
-      <c r="A31" s="594" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="1223">
+      <c r="A36" s="594" t="inlineStr">
         <is>
           <t>FUENTES Y NOTAS METODOLÓGICAS</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customFormat="1" customHeight="1" s="202">
-      <c r="A32" s="203" t="inlineStr">
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="202">
+      <c r="A37" s="203" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B32" s="201" t="n"/>
-      <c r="C32" s="201" t="n"/>
-      <c r="D32" s="201" t="n"/>
-      <c r="E32" s="342">
+      <c r="B37" s="201" t="n"/>
+      <c r="C37" s="201" t="n"/>
+      <c r="D37" s="201" t="n"/>
+      <c r="E37" s="342">
         <f>E4</f>
         <v/>
-      </c>
-    </row>
-    <row r="33" ht="25.5" customHeight="1" s="1223">
-      <c r="A33" s="591" t="inlineStr">
-        <is>
-          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25.5" customHeight="1" s="1223">
-      <c r="A34" s="591" t="inlineStr">
-        <is>
-          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="25.5" customHeight="1" s="1223">
-      <c r="A35" s="591" t="inlineStr">
-        <is>
-          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="25.5" customHeight="1" s="1223">
-      <c r="A36" s="591" t="inlineStr">
-        <is>
-          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25.5" customHeight="1" s="1223">
-      <c r="A37" s="591" t="inlineStr">
-        <is>
-          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
-        </is>
       </c>
     </row>
     <row r="38" ht="25.5" customHeight="1" s="1223">
       <c r="A38" s="591" t="inlineStr">
         <is>
-          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25.5" customHeight="1" s="1223">
       <c r="A39" s="591" t="inlineStr">
         <is>
-          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25.5" customHeight="1" s="1223">
       <c r="A40" s="591" t="inlineStr">
         <is>
-          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25.5" customHeight="1" s="1223">
       <c r="A41" s="591" t="inlineStr">
         <is>
-          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25.5" customHeight="1" s="1223">
       <c r="A42" s="591" t="inlineStr">
         <is>
+          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25.5" customHeight="1" s="1223">
+      <c r="A43" s="591" t="inlineStr">
+        <is>
+          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="25.5" customHeight="1" s="1223">
+      <c r="A44" s="591" t="inlineStr">
+        <is>
+          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25.5" customHeight="1" s="1223">
+      <c r="A45" s="591" t="inlineStr">
+        <is>
+          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25.5" customHeight="1" s="1223">
+      <c r="A46" s="591" t="inlineStr">
+        <is>
+          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25.5" customHeight="1" s="1223">
+      <c r="A47" s="591" t="inlineStr">
+        <is>
           <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
     <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="B12:E12"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A33:E33"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B11:E11"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A8:E8"/>
     <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C24:E24"/>
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="169">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1228,6 +1228,11 @@
       <name val="Calibri"/>
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="76">
@@ -6573,7 +6578,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9798,6 +9803,9 @@
     </xf>
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10730,7 +10738,7 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B9" s="100" t="n"/>
+      <c r="B9" s="1307" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="99" t="inlineStr">
@@ -10738,13 +10746,13 @@
           <t>No de Contrato</t>
         </is>
       </c>
-      <c r="B10" s="100" t="n"/>
+      <c r="B10" s="1307" t="n"/>
       <c r="C10" s="99" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="D10" s="100" t="n"/>
+      <c r="D10" s="1307" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="99" t="inlineStr">
@@ -10752,7 +10760,7 @@
           <t>Contratista</t>
         </is>
       </c>
-      <c r="B11" s="100" t="n"/>
+      <c r="B11" s="1307" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="99" t="inlineStr">
@@ -10760,7 +10768,7 @@
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="100" t="n"/>
+      <c r="B12" s="1307" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="1223">
       <c r="A13" s="597" t="inlineStr">
@@ -11134,6 +11142,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11165,13 +11174,12 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -23,8 +23,9 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1233,6 +1234,10 @@
       <name val="Calibri"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="76">
@@ -1684,7 +1689,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6569,6 +6574,20 @@
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6578,7 +6597,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1308">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9806,6 +9825,19 @@
     </xf>
     <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10622,7 +10654,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11142,7 +11173,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11175,8 +11205,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -10401,31 +10401,6 @@
     </a:ln>
   </spPr>
 </chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -14,18 +14,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
-    <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
-    <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+  <numFmts count="10">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;$ &quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="\$\ #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="171" formatCode="\$\ #,##0"/>
     <numFmt numFmtId="172" formatCode="$ #,##0"/>
+    <numFmt numFmtId="173" formatCode="&quot;$ &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="170">
+  <fonts count="168">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -635,13 +636,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF17365D"/>
-      <sz val="14"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
@@ -1149,28 +1143,9 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF17365D"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1227,17 +1202,27 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="8"/>
     </font>
     <font>
       <color rgb="008A8F99"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="76">
@@ -1689,7 +1674,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="412">
+  <borders count="423">
     <border>
       <left/>
       <right/>
@@ -2887,17 +2872,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
@@ -5820,21 +5794,6 @@
         <color theme="0"/>
       </left>
       <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
         <color theme="0" tint="-0.249946592608417"/>
       </right>
       <top style="thin">
@@ -6184,12 +6143,121 @@
       <left style="thin">
         <color rgb="FF002060"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
         <color rgb="FF002060"/>
-      </top>
-      <bottom style="thin">
+      </right>
+      <top style="thin">
         <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7C3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9A227"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9A227"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9A227"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6203,6 +6271,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
         <color rgb="FF17365D"/>
       </left>
@@ -6285,21 +6379,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF002060"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF002060"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF002060"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF002060"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -6340,35 +6419,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="4" tint="0.5998718222602009"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.5998718222602009"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color theme="4" tint="0.5999633777886288"/>
@@ -6381,6 +6431,17 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color theme="4" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFB7C3D0"/>
       </right>
@@ -6391,16 +6452,39 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB7C3D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF002060"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF002060"/>
-      </bottom>
+      <left style="thin">
+        <color theme="4" tint="0.5998718222602009"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.5998718222602009"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9A227"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -6576,18 +6660,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB8C2CC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB8C2CC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB8C2CC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB8C2CC"/>
-      </bottom>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6597,7 +6700,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1313">
+  <cellXfs count="1470">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -6750,28 +6853,28 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6790,15 +6893,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="40" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="40" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="40" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -6810,9 +6913,6 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6840,13 +6940,10 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
@@ -6856,7 +6953,7 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6901,15 +6998,15 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="27" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6937,9 +7034,6 @@
     <xf numFmtId="0" fontId="81" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="45" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -6949,21 +7043,21 @@
     <xf numFmtId="0" fontId="9" fillId="43" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="43" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="9" fillId="43" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="48" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -6976,10 +7070,10 @@
     <xf numFmtId="0" fontId="21" fillId="47" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6988,58 +7082,58 @@
     <xf numFmtId="0" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -7048,46 +7142,46 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="109" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="110" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="111" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="111" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="91" fillId="20" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="20" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="28" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7102,25 +7196,25 @@
     <xf numFmtId="0" fontId="66" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="57" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="58" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="84" fillId="58" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="58" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7139,117 +7233,114 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="53" borderId="174" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="53" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="53" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="2" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="127" fillId="55" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="69" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="69" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="18" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="242" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="240" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="60" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7267,15 +7358,15 @@
     <xf numFmtId="0" fontId="59" fillId="18" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="150" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="149" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7285,34 +7376,34 @@
     <xf numFmtId="4" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="101" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7320,64 +7411,64 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="154" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="153" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="25" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="73" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="135" fillId="25" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="73" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="17" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="16" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="28" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="74" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="17" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="16" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="74" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="28" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="74" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="74" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="17" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="16" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="25" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="25" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -7392,22 +7483,21 @@
     <xf numFmtId="0" fontId="55" fillId="25" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="42" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7415,33 +7505,33 @@
     <xf numFmtId="0" fontId="38" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="42" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="146" fillId="42" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7451,80 +7541,80 @@
     <xf numFmtId="0" fontId="38" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="25" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="25" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="25" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -7533,19 +7623,19 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="39" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7554,27 +7644,19 @@
     <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="16" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7583,37 +7665,25 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7621,44 +7691,183 @@
     <xf numFmtId="0" fontId="64" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="28" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="25" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="97" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="28" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="164" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="59" fillId="19" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="18" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="25" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="163" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="159" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7668,10 +7877,13 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -7682,10 +7894,10 @@
     <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7698,23 +7910,29 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="41" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="41" borderId="186" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7754,10 +7972,6 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -7768,337 +7982,294 @@
     <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="164" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="28" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="157" fillId="3" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="155" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="87" fillId="49" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="55" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="25" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="25" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="50" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="104" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="70" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="60" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="128" fillId="70" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="135" fillId="25" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="96" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="28" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="155" fillId="3" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="155" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="154" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="86" fillId="49" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="163" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="123" fillId="17" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="163" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="16" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="154" fillId="26" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="28" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="25" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="28" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="127" fillId="55" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="44" fillId="18" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="44" fillId="18" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="59" fillId="19" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="18" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="155" fillId="26" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="25" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="116" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="28" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="52" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="162" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="49" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="28" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="28" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="41" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="53" fillId="41" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="163" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8108,150 +8279,150 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="93" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="42" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="234" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="132" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="61" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="133" fillId="71" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="133" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="61" borderId="239" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="134" fillId="71" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="259" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="43" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="43" borderId="233" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="61" borderId="239" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="66" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="60" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="60" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="61" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="28" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="142" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="136" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8262,26 +8433,29 @@
     <xf numFmtId="0" fontId="66" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="25" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="25" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="75" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="62" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8290,29 +8464,41 @@
     <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="128" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="128" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="109" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="193" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="49" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="370" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="371" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="55" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="194" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8321,49 +8507,45 @@
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="101" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="100" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="95" fillId="34" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="109" fillId="20" borderId="195" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="196" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="152" fillId="3" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="99" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="34" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="20" borderId="194" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="20" borderId="195" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="42" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8375,17 +8557,17 @@
     <xf numFmtId="0" fontId="43" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="3" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="3" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="80" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8397,17 +8579,17 @@
     <xf numFmtId="0" fontId="73" fillId="38" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="34" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8419,35 +8601,43 @@
     <xf numFmtId="0" fontId="82" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="28" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="107" fillId="28" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="199" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8462,50 +8652,54 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="206" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="104" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="376" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="378" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
@@ -8513,72 +8707,81 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="202" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
@@ -8589,12 +8792,13 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="40" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8605,181 +8809,181 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="26" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="170" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="26" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="171" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="176" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="41" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="121" fillId="56" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="28" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="56" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="161" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="28" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="28" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="211" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="121" fillId="28" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="28" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="28" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="214" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="171" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="170" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="125" fillId="41" borderId="186" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="211" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8804,7 +9008,7 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8812,13 +9016,16 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="53" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8831,8 +9038,8 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="58" fillId="34" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8842,15 +9049,15 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8863,29 +9070,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="20" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="232" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8900,11 +9107,11 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="107" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="21" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8917,14 +9124,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -8946,13 +9153,13 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="227" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="228" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8969,20 +9176,20 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="199" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="222" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -9002,7 +9209,7 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -9024,11 +9231,11 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="11" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -9060,84 +9267,84 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="226" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="227" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="30" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="30" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="24" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="29" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="29" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9150,20 +9357,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -9173,10 +9380,10 @@
     <xf numFmtId="0" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="242" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9188,16 +9395,16 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="88" fillId="14" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9207,11 +9414,14 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -9219,150 +9429,153 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="57" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="38" fillId="16" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="16" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="51" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="51" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="51" fillId="16" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="51" fillId="16" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="88" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="87" fillId="24" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9371,29 +9584,29 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9413,16 +9626,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9434,30 +9647,30 @@
     <xf numFmtId="0" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="14" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="15" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9466,10 +9679,10 @@
     <xf numFmtId="0" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="49" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9479,18 +9692,21 @@
     <xf numFmtId="0" fontId="49" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9499,23 +9715,23 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9524,321 +9740,605 @@
     <xf numFmtId="0" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="39" fillId="3" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="22" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="3" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="49" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="49" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="383" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="96" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="28" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="155" fillId="3" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="155" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="154" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="86" fillId="49" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="50" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="69" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="374" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="17" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="26" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="56" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="105" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="372" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="3" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="49" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="70" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="70" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="132" fillId="60" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="66" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="25" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="28" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="157" fillId="3" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="155" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="87" fillId="49" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="66" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="49" borderId="384" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="59" fillId="19" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="420" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="51" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="51" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="16" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="18" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="420" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="60" fillId="22" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="39" fillId="3" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="422" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9968,439 +10468,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10634,510 +10701,510 @@
   <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="42" customWidth="1" style="1223" min="1" max="1"/>
-    <col width="20.77734375" customWidth="1" style="1223" min="2" max="2"/>
-    <col width="50.77734375" customWidth="1" style="1223" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="1223" min="4" max="5"/>
+    <col width="42" customWidth="1" style="550" min="1" max="1"/>
+    <col width="20.77734375" customWidth="1" style="550" min="2" max="2"/>
+    <col width="50.77734375" customWidth="1" style="550" min="3" max="3"/>
+    <col width="15.77734375" customWidth="1" style="550" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="1223">
+    <row r="1" ht="25.5" customHeight="1" s="550">
       <c r="A1" s="3" t="n"/>
-      <c r="B1" s="598" t="inlineStr">
+      <c r="B1" s="560" t="inlineStr">
         <is>
           <t>FICHA TÉCNICA DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="4.95" customHeight="1" s="1223">
+    <row r="2" ht="4.95" customHeight="1" s="550">
       <c r="A2" s="4" t="n"/>
-      <c r="B2" s="595" t="n"/>
-      <c r="C2" s="596" t="n"/>
-      <c r="D2" s="596" t="n"/>
-      <c r="E2" s="596" t="n"/>
+      <c r="B2" s="556" t="n"/>
+      <c r="C2" s="557" t="n"/>
+      <c r="D2" s="557" t="n"/>
+      <c r="E2" s="557" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="1223">
+    <row r="3" ht="18" customHeight="1" s="550">
       <c r="A3" s="4" t="n"/>
-      <c r="B3" s="186" t="n"/>
-      <c r="C3" s="187" t="n"/>
-      <c r="D3" s="549" t="inlineStr">
+      <c r="B3" s="183" t="n"/>
+      <c r="C3" s="184" t="n"/>
+      <c r="D3" s="558" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="E3" s="551" t="n"/>
+      <c r="E3" s="559" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="1223">
+    <row r="4" ht="15" customHeight="1" s="550">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="600" t="inlineStr">
+      <c r="B4" s="564" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="C4" s="546" t="n"/>
-      <c r="D4" s="96" t="inlineStr">
+      <c r="C4" s="562" t="n"/>
+      <c r="D4" s="94" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="E4" s="1161" t="inlineStr">
+      <c r="E4" s="1209" t="inlineStr">
         <is>
           <t>RYR-FT-001</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="1223">
+    <row r="5" ht="15" customHeight="1" s="550">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="599" t="inlineStr">
+      <c r="B5" s="561" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
         </is>
       </c>
-      <c r="C5" s="546" t="n"/>
-      <c r="D5" s="96" t="inlineStr">
+      <c r="C5" s="562" t="n"/>
+      <c r="D5" s="94" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="E5" s="1147" t="n">
+      <c r="E5" s="1195" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="1223">
+    <row r="6" ht="15" customHeight="1" s="550">
       <c r="A6" s="4" t="n"/>
-      <c r="B6" s="188" t="n"/>
-      <c r="C6" s="189" t="n"/>
-      <c r="D6" s="96" t="inlineStr">
+      <c r="B6" s="185" t="n"/>
+      <c r="C6" s="186" t="n"/>
+      <c r="D6" s="94" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="E6" s="168" t="inlineStr">
+      <c r="E6" s="165" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="1223">
-      <c r="B7" s="188" t="n"/>
-      <c r="C7" s="189" t="n"/>
-      <c r="D7" s="97" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="550">
+      <c r="B7" s="185" t="n"/>
+      <c r="C7" s="186" t="n"/>
+      <c r="D7" s="95" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="E7" s="1191" t="inlineStr">
+      <c r="E7" s="1240" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="597" t="inlineStr">
+      <c r="A8" s="563" t="inlineStr">
         <is>
           <t>IDENTIFICACIÓN DEL PROYECTO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="99" t="inlineStr">
+      <c r="A9" s="97" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B9" s="1307" t="n"/>
+      <c r="B9" s="552" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="97" t="inlineStr">
         <is>
           <t>No de Contrato</t>
         </is>
       </c>
-      <c r="B10" s="1307" t="n"/>
-      <c r="C10" s="99" t="inlineStr">
+      <c r="B10" s="552" t="n"/>
+      <c r="C10" s="97" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="D10" s="1307" t="n"/>
+      <c r="D10" s="552" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="99" t="inlineStr">
+      <c r="A11" s="97" t="inlineStr">
         <is>
           <t>Contratista</t>
         </is>
       </c>
-      <c r="B11" s="1307" t="n"/>
+      <c r="B11" s="552" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="99" t="inlineStr">
+      <c r="A12" s="97" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="1307" t="n"/>
+      <c r="B12" s="552" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="1223">
-      <c r="A13" s="597" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="550">
+      <c r="A13" s="563" t="inlineStr">
         <is>
           <t>DATOS GENERALES DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="1223">
-      <c r="A14" s="99" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="550">
+      <c r="A14" s="97" t="inlineStr">
         <is>
           <t>Número de pisos (torre)</t>
         </is>
       </c>
-      <c r="B14" s="100" t="n"/>
-      <c r="C14" s="593" t="inlineStr">
+      <c r="B14" s="98" t="n"/>
+      <c r="C14" s="549" t="inlineStr">
         <is>
           <t>pisos</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="1223">
-      <c r="A15" s="101" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="550">
+      <c r="A15" s="99" t="inlineStr">
         <is>
           <t>Número de sótanos (parqueaderos)</t>
         </is>
       </c>
-      <c r="B15" s="102" t="n"/>
-      <c r="C15" s="590" t="inlineStr">
+      <c r="B15" s="100" t="n"/>
+      <c r="C15" s="554" t="inlineStr">
         <is>
           <t>niveles</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="1223">
-      <c r="A16" s="99" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="550">
+      <c r="A16" s="97" t="inlineStr">
         <is>
           <t>Área del lote</t>
         </is>
       </c>
-      <c r="B16" s="100" t="n"/>
-      <c r="C16" s="593" t="inlineStr">
+      <c r="B16" s="98" t="n"/>
+      <c r="C16" s="549" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="1223">
-      <c r="A17" s="101" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="550">
+      <c r="A17" s="99" t="inlineStr">
         <is>
           <t>Área construida típica por piso</t>
         </is>
       </c>
-      <c r="B17" s="102" t="n"/>
-      <c r="C17" s="590" t="inlineStr">
+      <c r="B17" s="100" t="n"/>
+      <c r="C17" s="554" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="1223">
-      <c r="A18" s="99" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="550">
+      <c r="A18" s="97" t="inlineStr">
         <is>
           <t>Área construida - torre (12 pisos)</t>
         </is>
       </c>
-      <c r="B18" s="103">
+      <c r="B18" s="101">
         <f>B14*B17</f>
         <v/>
       </c>
-      <c r="C18" s="593" t="inlineStr">
+      <c r="C18" s="549" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="1223">
-      <c r="A19" s="101" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="550">
+      <c r="A19" s="99" t="inlineStr">
         <is>
           <t>Área construida - sótanos (2 niveles)</t>
         </is>
       </c>
-      <c r="B19" s="102" t="n"/>
-      <c r="C19" s="590" t="inlineStr">
+      <c r="B19" s="100" t="n"/>
+      <c r="C19" s="554" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="1223">
-      <c r="A20" s="99" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="550">
+      <c r="A20" s="97" t="inlineStr">
         <is>
           <t>Área cubierta / cuarto de máquinas / tanques</t>
         </is>
       </c>
-      <c r="B20" s="100" t="n"/>
-      <c r="C20" s="593" t="inlineStr">
+      <c r="B20" s="98" t="n"/>
+      <c r="C20" s="549" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="1223">
-      <c r="A21" s="101" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="550">
+      <c r="A21" s="99" t="inlineStr">
         <is>
           <t>ÁREA TOTAL CONSTRUIDA</t>
         </is>
       </c>
-      <c r="B21" s="104">
+      <c r="B21" s="102">
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="590" t="inlineStr">
+      <c r="C21" s="554" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="1223">
-      <c r="A22" s="99" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="550">
+      <c r="A22" s="97" t="inlineStr">
         <is>
           <t>Número de apartamentos</t>
         </is>
       </c>
-      <c r="B22" s="100" t="n"/>
-      <c r="C22" s="593" t="inlineStr">
+      <c r="B22" s="98" t="n"/>
+      <c r="C22" s="549" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="1223">
-      <c r="A23" s="101" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="550">
+      <c r="A23" s="99" t="inlineStr">
         <is>
           <t>Área promedio por apartamento (vendible)</t>
         </is>
       </c>
-      <c r="B23" s="102" t="n"/>
-      <c r="C23" s="590" t="inlineStr">
+      <c r="B23" s="100" t="n"/>
+      <c r="C23" s="554" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="1223">
-      <c r="A24" s="99" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="550">
+      <c r="A24" s="97" t="inlineStr">
         <is>
           <t>Número de parqueaderos</t>
         </is>
       </c>
-      <c r="B24" s="100" t="n"/>
-      <c r="C24" s="593" t="inlineStr">
+      <c r="B24" s="98" t="n"/>
+      <c r="C24" s="549" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="1223">
-      <c r="A25" s="101" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="550">
+      <c r="A25" s="99" t="inlineStr">
         <is>
           <t>Número de ascensores</t>
         </is>
       </c>
-      <c r="B25" s="102" t="n"/>
-      <c r="C25" s="590" t="inlineStr">
+      <c r="B25" s="100" t="n"/>
+      <c r="C25" s="554" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="1223">
-      <c r="A26" s="99" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="550">
+      <c r="A26" s="97" t="inlineStr">
         <is>
           <t>Altura total aproximada (sótano a cubierta)</t>
         </is>
       </c>
-      <c r="B26" s="100" t="n"/>
-      <c r="C26" s="593" t="inlineStr">
+      <c r="B26" s="98" t="n"/>
+      <c r="C26" s="549" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="592" t="n"/>
-      <c r="B27" s="592" t="n"/>
-      <c r="C27" s="592" t="n"/>
+      <c r="A27" s="555" t="n"/>
+      <c r="B27" s="555" t="n"/>
+      <c r="C27" s="555" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="1223">
-      <c r="A28" s="594" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="550">
+      <c r="A28" s="553" t="inlineStr">
         <is>
           <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="1223">
-      <c r="A29" s="99" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="550">
+      <c r="A29" s="97" t="inlineStr">
         <is>
           <t>Administración (A)</t>
         </is>
       </c>
-      <c r="B29" s="466" t="n">
+      <c r="B29" s="1283" t="n">
         <v>0.1</v>
       </c>
-      <c r="C29" s="593" t="inlineStr">
+      <c r="C29" s="549" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="1223">
-      <c r="A30" s="101" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="550">
+      <c r="A30" s="99" t="inlineStr">
         <is>
           <t>Imprevistos (I)</t>
         </is>
       </c>
-      <c r="B30" s="467" t="n">
+      <c r="B30" s="1284" t="n">
         <v>0.04</v>
       </c>
-      <c r="C30" s="590" t="inlineStr">
+      <c r="C30" s="554" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="1223">
-      <c r="A31" s="99" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="550">
+      <c r="A31" s="97" t="inlineStr">
         <is>
           <t>Utilidad (U)</t>
         </is>
       </c>
-      <c r="B31" s="466" t="n">
+      <c r="B31" s="1283" t="n">
         <v>0.12</v>
       </c>
-      <c r="C31" s="593" t="inlineStr">
+      <c r="C31" s="549" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="1223">
-      <c r="A32" s="101" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="550">
+      <c r="A32" s="99" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="B32" s="467" t="n">
+      <c r="B32" s="1284" t="n">
         <v>0.19</v>
       </c>
-      <c r="C32" s="590" t="inlineStr">
+      <c r="C32" s="554" t="inlineStr">
         <is>
           <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="592" t="n"/>
-      <c r="B33" s="592" t="n"/>
-      <c r="C33" s="592" t="n"/>
+      <c r="A33" s="555" t="n"/>
+      <c r="B33" s="555" t="n"/>
+      <c r="C33" s="555" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="1223">
-      <c r="A34" s="105" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="550">
+      <c r="A34" s="103" t="inlineStr">
         <is>
           <t>AIU TOTAL (A+I+U)</t>
         </is>
       </c>
-      <c r="B34" s="468">
+      <c r="B34" s="1285">
         <f>B29+B30+B31</f>
         <v/>
       </c>
-      <c r="C34" s="592" t="n"/>
+      <c r="C34" s="555" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="592" t="n"/>
-      <c r="B35" s="592" t="n"/>
-      <c r="C35" s="592" t="n"/>
+      <c r="A35" s="555" t="n"/>
+      <c r="B35" s="555" t="n"/>
+      <c r="C35" s="555" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="1223">
-      <c r="A36" s="594" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="550">
+      <c r="A36" s="553" t="inlineStr">
         <is>
           <t>FUENTES Y NOTAS METODOLÓGICAS</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customFormat="1" customHeight="1" s="202">
-      <c r="A37" s="203" t="inlineStr">
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="199">
+      <c r="A37" s="200" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B37" s="201" t="n"/>
-      <c r="C37" s="201" t="n"/>
-      <c r="D37" s="201" t="n"/>
-      <c r="E37" s="342">
+      <c r="B37" s="198" t="n"/>
+      <c r="C37" s="198" t="n"/>
+      <c r="D37" s="198" t="n"/>
+      <c r="E37" s="337">
         <f>E4</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="25.5" customHeight="1" s="1223">
-      <c r="A38" s="591" t="inlineStr">
+    <row r="38" ht="25.5" customHeight="1" s="550">
+      <c r="A38" s="551" t="inlineStr">
         <is>
           <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="25.5" customHeight="1" s="1223">
-      <c r="A39" s="591" t="inlineStr">
+    <row r="39" ht="25.5" customHeight="1" s="550">
+      <c r="A39" s="551" t="inlineStr">
         <is>
           <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="25.5" customHeight="1" s="1223">
-      <c r="A40" s="591" t="inlineStr">
+    <row r="40" ht="25.5" customHeight="1" s="550">
+      <c r="A40" s="551" t="inlineStr">
         <is>
           <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="25.5" customHeight="1" s="1223">
-      <c r="A41" s="591" t="inlineStr">
+    <row r="41" ht="25.5" customHeight="1" s="550">
+      <c r="A41" s="551" t="inlineStr">
         <is>
           <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="25.5" customHeight="1" s="1223">
-      <c r="A42" s="591" t="inlineStr">
+    <row r="42" ht="25.5" customHeight="1" s="550">
+      <c r="A42" s="551" t="inlineStr">
         <is>
           <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="25.5" customHeight="1" s="1223">
-      <c r="A43" s="591" t="inlineStr">
+    <row r="43" ht="25.5" customHeight="1" s="550">
+      <c r="A43" s="551" t="inlineStr">
         <is>
           <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="25.5" customHeight="1" s="1223">
-      <c r="A44" s="591" t="inlineStr">
+    <row r="44" ht="25.5" customHeight="1" s="550">
+      <c r="A44" s="551" t="inlineStr">
         <is>
           <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="25.5" customHeight="1" s="1223">
-      <c r="A45" s="591" t="inlineStr">
+    <row r="45" ht="25.5" customHeight="1" s="550">
+      <c r="A45" s="551" t="inlineStr">
         <is>
           <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="25.5" customHeight="1" s="1223">
-      <c r="A46" s="591" t="inlineStr">
+    <row r="46" ht="25.5" customHeight="1" s="550">
+      <c r="A46" s="551" t="inlineStr">
         <is>
           <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="25.5" customHeight="1" s="1223">
-      <c r="A47" s="591" t="inlineStr">
+    <row r="47" ht="25.5" customHeight="1" s="550">
+      <c r="A47" s="551" t="inlineStr">
         <is>
           <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
         </is>
@@ -11148,6 +11215,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11173,16 +11241,15 @@
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="C33:E33"/>
+    <mergeCell ref="B1:E1"/>
     <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B1:E1"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ficha Técnica del Proyecto" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -10471,32 +10472,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>69253</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>174506</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>69253</colOff>
+      <row>6</row>
+      <rowOff>174506</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2952000" cy="1368000"/>
@@ -10508,11 +10509,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10711,7 +10712,7 @@
       <c r="A1" s="3" t="n"/>
       <c r="B1" s="560" t="inlineStr">
         <is>
-          <t>FICHA TÉCNICA DEL PROYECTO</t>
+          <t>FICHA TÉCNICA DEL PROYECTO — EDIFICACIÓN Y REFORMAS</t>
         </is>
       </c>
     </row>
@@ -11215,7 +11216,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11248,8 +11248,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -10472,32 +10472,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>69253</colOff>
-      <row>6</row>
-      <rowOff>174506</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>69253</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>174506</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2952000" cy="1368000"/>
@@ -10509,11 +10509,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-ficha.xlsx
+++ b/public/plantilla-ficha.xlsx
@@ -9,31 +9,43 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;$ &quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="\$\ #,##0.00"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="171" formatCode="\$\ #,##0"/>
-    <numFmt numFmtId="172" formatCode="$ #,##0"/>
-    <numFmt numFmtId="173" formatCode="&quot;$ &quot;#,##0.00"/>
+  <numFmts count="8">
+    <numFmt numFmtId="164" formatCode="\$\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="169" formatCode="\$\ #,##0.00"/>
+    <numFmt numFmtId="170" formatCode="&quot;$ &quot;#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="&quot;$ &quot;#,##0"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -1203,30 +1215,37 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <color rgb="008A8F99"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="76">
+  <fills count="78">
     <fill>
       <patternFill/>
     </fill>
@@ -1674,8 +1693,20 @@
         <bgColor rgb="FF1B2A45"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFEAF0F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor rgb="FFEAF0F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="423">
+  <borders count="394">
     <border>
       <left/>
       <right/>
@@ -4863,19 +4894,6 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color theme="4" tint="0.5999633777886288"/>
       </right>
       <top style="thin">
@@ -5854,19 +5872,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thick">
         <color rgb="FF17365D"/>
@@ -6263,633 +6268,372 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF17365D"/>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD39A12"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD39A12"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD39A12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD39A12"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD39A12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD39A12"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD39A12"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD39A12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.0499893185216834"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.0499893185216834"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.0499893185216834"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.0499893185216834"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.0499893185216834"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.0499893185216834"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF17365D"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD9E1F2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9E1F2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E1F2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9E1F2"/>
-      </right>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9E1F2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF002060"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF002060"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF002060"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB7C3D0"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB7C3D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF002060"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.5998718222602009"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.5998718222602009"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC9A227"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFC9A227"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB8C2CC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF142B44"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF142B44"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB8C2CC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB8C2CC"/>
-      </right>
-      <top style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.3999450666829432"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.3999450666829432"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="5">
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+  <cellStyleXfs count="7">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1470">
+  <cellXfs count="1384">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="32" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="32" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="57" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="57" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="72" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="66" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="5" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -6899,974 +6643,897 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="40" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="40" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="40" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="35" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="20" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="40" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="40" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="40" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="26" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="51" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="55" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="27" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="75" fillId="27" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="83" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="45" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="45" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="43" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="43" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="43" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="43" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="48" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="48" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="28" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="105" fillId="28" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="28" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="105" fillId="28" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="23" fillId="46" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="47" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="46" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="72" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="72" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="57" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="57" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="110" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="111" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="111" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="112" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="91" fillId="20" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="20" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="93" fillId="20" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="20" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="28" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="28" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="5" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="28" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="28" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="58" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="58" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="34" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="57" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="57" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="57" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="58" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="58" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="34" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="122" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="124" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="53" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="53" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="118" fillId="53" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="120" fillId="53" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="2" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="2" fontId="128" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="128" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="124" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="69" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="69" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="240" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="26" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="26" borderId="240" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="74" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="18" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="26" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="155" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="25" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="73" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="17" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="16" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="28" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="74" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="17" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="16" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="74" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="17" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="16" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="25" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="25" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="10" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="10" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="42" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="10" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="74" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="18" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="58" fillId="18" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="25" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="25" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="284" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="26" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="26" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="5" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="5" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="28" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="28" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="125" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="125" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="100" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="153" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="25" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="73" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="17" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="145" fillId="25" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="25" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="50" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="16" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="28" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="70" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="60" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="70" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="137" fillId="25" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="125" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="125" fillId="17" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="74" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="17" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="16" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="125" fillId="28" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="74" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="25" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="25" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="25" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="25" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="42" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="42" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="25" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="25" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="64" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="28" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="164" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="59" fillId="19" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="18" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="25" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="165" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="25" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="159" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="161" fillId="28" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7875,403 +7542,694 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="281" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="41" borderId="186" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="125" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="28" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="75" fillId="41" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="41" borderId="186" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="28" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="77" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="77" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="51" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="28" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="99" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="157" fillId="3" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="156" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="88" fillId="49" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="40" fillId="17" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="40" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="138" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="138" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="139" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="139" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="50" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="65" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="64" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="51" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="51" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="57" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="72" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="45" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="45" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="72" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="57" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="45" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="46" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="47" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="45" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="45" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="45" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="125" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="128" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="128" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="125" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="125" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="125" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="125" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="50" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="50" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="50" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="18" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="50" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="50" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="46" fillId="18" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="51" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="61" fillId="19" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="36" fillId="18" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="38" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="59" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="98" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="138" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="139" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="139" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="77" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="168" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="64" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="57" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="65" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="68" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="89" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="89" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="64" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="57" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="89" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="261" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="51" fillId="3" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="392" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="165" fontId="77" fillId="76" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="76" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="392" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="165" fontId="77" fillId="77" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="6" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="77" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="4" fontId="77" fillId="6" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="6" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="76" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="76" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="6" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="76" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="169" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="28" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="28" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="393" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="4" fontId="77" fillId="77" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="77" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="77" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="76" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="76" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="76" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="76" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="77" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="77" fillId="77" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="165" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="169" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="94" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="393" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="393" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="57" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="25" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="49" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="25" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="25" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="50" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="104" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="28" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="160" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="41" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="161" fillId="28" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="349" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="26" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="380" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="156" fillId="26" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="70" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="60" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="16" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="70" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="135" fillId="25" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="96" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="38" fillId="28" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="155" fillId="3" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="155" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="154" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="86" fillId="49" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="38" fillId="17" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="163" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="123" fillId="17" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="28" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="76" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="163" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="101" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="96" fillId="16" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="154" fillId="26" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="28" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="25" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="115" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="28" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="96" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="28" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="344" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="28" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="41" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="55" fillId="41" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8280,68 +8238,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="111" fillId="42" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="237" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="234" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="132" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="61" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="133" fillId="71" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="383" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="71" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8350,283 +8295,371 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="259" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="43" borderId="233" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="43" borderId="233" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="66" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="60" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="60" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="66" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="60" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="61" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="134" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="61" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="60" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="281" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="61" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="112" fillId="28" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="137" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="144" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="384" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="368" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="369" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="64" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="389" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="390" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="391" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="72" borderId="388" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="387" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="385" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="386" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="68" fillId="49" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="49" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="368" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="369" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="35" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="25" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="142" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="75" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="110" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="62" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="25" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="102" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="49" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="368" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="369" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="3" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="193" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="75" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="62" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="193" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="100" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="49" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="370" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="371" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="3" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="99" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="94" fillId="34" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="108" fillId="20" borderId="194" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="20" borderId="195" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="42" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="64" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="64" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="48" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="34" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="20" borderId="194" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="20" borderId="195" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="3" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="51" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="34" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="3" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="82" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="28" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="105" fillId="28" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="83" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="72" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="75" fillId="38" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="38" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="34" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="83" fillId="20" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="109" fillId="28" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="51" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="20" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="107" fillId="28" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="51" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8639,7 +8672,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="199" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8650,10 +8683,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="206" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="206" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8661,169 +8694,177 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="374" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="375" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="376" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="378" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="40" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="26" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="40" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="24" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="371" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="26" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="26" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="54" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8831,1522 +8872,997 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="170" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="170" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="125" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="28" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="28" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="121" fillId="56" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="123" fillId="56" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="28" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="17" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="163" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="125" fillId="54" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="28" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="28" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="211" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="372" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="41" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="28" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="28" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="28" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="28" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="119" fillId="28" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="211" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="28" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="170" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="41" borderId="186" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="127" fillId="41" borderId="186" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="170" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="53" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="28" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="116" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="20" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="62" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="229" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="34" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="60" fillId="34" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="27" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="73" fillId="31" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="20" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="62" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="232" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="40" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="106" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="73" fillId="31" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="60" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="224" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="227" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="228" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="2" fontId="40" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="11" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="11" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="31" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="8" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="40" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="8" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="25" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="11" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="3" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="8" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="8" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="103" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="11" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="23" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="225" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="226" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="30" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="16" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="16" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="24" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="24" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="29" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="14" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="50" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="3" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="30" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="51" fillId="3" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="30" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="50" fillId="0" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="22" borderId="242" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="22" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="50" fillId="0" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="21" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="30" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="49" fillId="3" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="21" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="57" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="22" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="34" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="24" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="67" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="67" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="21" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="40" fillId="16" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="55" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="53" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="53" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="30" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="3" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="3" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="34" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="50" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="21" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="16" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="21" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="25" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="29" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="38" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="30" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="38" fillId="0" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="242" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="14" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="14" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="3" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="25" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="30" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="58" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="58" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="30" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="55" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="57" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="16" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="51" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="51" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="24" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="16" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="62" fillId="22" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="321" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="60" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="22" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="3" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="58" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="36" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="14" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="3" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="49" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="49" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="383" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="96" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="38" fillId="28" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="155" fillId="3" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="155" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="154" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="86" fillId="49" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="38" fillId="17" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="374" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="28" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="17" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="26" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="56" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="16" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="16" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="59" fillId="19" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="49" fillId="3" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="420" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="51" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="51" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="16" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="3" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="18" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="36" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="420" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="60" fillId="22" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="39" fillId="3" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="422" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="77" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="77" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="51" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
     <cellStyle name="Normal 3" xfId="2"/>
     <cellStyle name="Normal 4" xfId="3"/>
     <cellStyle name="Normal 5" xfId="4"/>
+    <cellStyle name="Normal 6" xfId="5"/>
+    <cellStyle name="Normal 7" xfId="6"/>
   </cellStyles>
   <dxfs count="7">
     <dxf>
@@ -10702,75 +10218,75 @@
   <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="42" customWidth="1" style="550" min="1" max="1"/>
-    <col width="20.77734375" customWidth="1" style="550" min="2" max="2"/>
-    <col width="50.77734375" customWidth="1" style="550" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="550" min="4" max="5"/>
+    <col width="42" customWidth="1" style="614" min="1" max="1"/>
+    <col width="20.77734375" customWidth="1" style="614" min="2" max="2"/>
+    <col width="50.77734375" customWidth="1" style="614" min="3" max="3"/>
+    <col width="15.77734375" customWidth="1" style="614" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="550">
+    <row r="1" ht="25.5" customHeight="1" s="614">
       <c r="A1" s="3" t="n"/>
-      <c r="B1" s="560" t="inlineStr">
+      <c r="B1" s="624" t="inlineStr">
         <is>
-          <t>FICHA TÉCNICA DEL PROYECTO — EDIFICACIÓN Y REFORMAS</t>
+          <t>FICHA TÉCNICA DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="4.95" customHeight="1" s="550">
+    <row r="2" ht="4.95" customHeight="1" s="614">
       <c r="A2" s="4" t="n"/>
-      <c r="B2" s="556" t="n"/>
-      <c r="C2" s="557" t="n"/>
-      <c r="D2" s="557" t="n"/>
-      <c r="E2" s="557" t="n"/>
+      <c r="B2" s="620" t="n"/>
+      <c r="C2" s="621" t="n"/>
+      <c r="D2" s="621" t="n"/>
+      <c r="E2" s="621" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="550">
+    <row r="3" ht="18" customHeight="1" s="614">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="183" t="n"/>
       <c r="C3" s="184" t="n"/>
-      <c r="D3" s="558" t="inlineStr">
+      <c r="D3" s="622" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="E3" s="559" t="n"/>
+      <c r="E3" s="623" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="550">
+    <row r="4" ht="15" customHeight="1" s="614">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="564" t="inlineStr">
+      <c r="B4" s="628" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="C4" s="562" t="n"/>
+      <c r="C4" s="626" t="n"/>
       <c r="D4" s="94" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="E4" s="1209" t="inlineStr">
+      <c r="E4" s="1333" t="inlineStr">
         <is>
           <t>RYR-FT-001</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="550">
+    <row r="5" ht="15" customHeight="1" s="614">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="561" t="inlineStr">
+      <c r="B5" s="625" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
         </is>
       </c>
-      <c r="C5" s="562" t="n"/>
+      <c r="C5" s="626" t="n"/>
       <c r="D5" s="94" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="E5" s="1195" t="n">
+      <c r="E5" s="1322" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="550">
+    <row r="6" ht="15" customHeight="1" s="614">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="185" t="n"/>
       <c r="C6" s="186" t="n"/>
@@ -10785,7 +10301,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="550">
+    <row r="7" ht="15" customHeight="1" s="614">
       <c r="B7" s="185" t="n"/>
       <c r="C7" s="186" t="n"/>
       <c r="D7" s="95" t="inlineStr">
@@ -10793,14 +10309,14 @@
           <t>Página</t>
         </is>
       </c>
-      <c r="E7" s="1240" t="inlineStr">
+      <c r="E7" s="1359" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="563" t="inlineStr">
+      <c r="A8" s="627" t="inlineStr">
         <is>
           <t>IDENTIFICACIÓN DEL PROYECTO</t>
         </is>
@@ -10812,7 +10328,7 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B9" s="552" t="n"/>
+      <c r="B9" s="619" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="97" t="inlineStr">
@@ -10820,13 +10336,13 @@
           <t>No de Contrato</t>
         </is>
       </c>
-      <c r="B10" s="552" t="n"/>
+      <c r="B10" s="619" t="n"/>
       <c r="C10" s="97" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="D10" s="552" t="n"/>
+      <c r="D10" s="619" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="97" t="inlineStr">
@@ -10834,7 +10350,7 @@
           <t>Contratista</t>
         </is>
       </c>
-      <c r="B11" s="552" t="n"/>
+      <c r="B11" s="619" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="97" t="inlineStr">
@@ -10842,68 +10358,68 @@
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="552" t="n"/>
+      <c r="B12" s="619" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="550">
-      <c r="A13" s="563" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="614">
+      <c r="A13" s="627" t="inlineStr">
         <is>
           <t>DATOS GENERALES DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="550">
+    <row r="14" ht="15" customHeight="1" s="614">
       <c r="A14" s="97" t="inlineStr">
         <is>
           <t>Número de pisos (torre)</t>
         </is>
       </c>
       <c r="B14" s="98" t="n"/>
-      <c r="C14" s="549" t="inlineStr">
+      <c r="C14" s="618" t="inlineStr">
         <is>
           <t>pisos</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="550">
+    <row r="15" ht="15" customHeight="1" s="614">
       <c r="A15" s="99" t="inlineStr">
         <is>
           <t>Número de sótanos (parqueaderos)</t>
         </is>
       </c>
       <c r="B15" s="100" t="n"/>
-      <c r="C15" s="554" t="inlineStr">
+      <c r="C15" s="613" t="inlineStr">
         <is>
           <t>niveles</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="550">
+    <row r="16" ht="15" customHeight="1" s="614">
       <c r="A16" s="97" t="inlineStr">
         <is>
           <t>Área del lote</t>
         </is>
       </c>
       <c r="B16" s="98" t="n"/>
-      <c r="C16" s="549" t="inlineStr">
+      <c r="C16" s="618" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="550">
+    <row r="17" ht="15" customHeight="1" s="614">
       <c r="A17" s="99" t="inlineStr">
         <is>
           <t>Área construida típica por piso</t>
         </is>
       </c>
       <c r="B17" s="100" t="n"/>
-      <c r="C17" s="554" t="inlineStr">
+      <c r="C17" s="613" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="550">
+    <row r="18" ht="15" customHeight="1" s="614">
       <c r="A18" s="97" t="inlineStr">
         <is>
           <t>Área construida - torre (12 pisos)</t>
@@ -10913,39 +10429,39 @@
         <f>B14*B17</f>
         <v/>
       </c>
-      <c r="C18" s="549" t="inlineStr">
+      <c r="C18" s="618" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="550">
+    <row r="19" ht="15" customHeight="1" s="614">
       <c r="A19" s="99" t="inlineStr">
         <is>
           <t>Área construida - sótanos (2 niveles)</t>
         </is>
       </c>
       <c r="B19" s="100" t="n"/>
-      <c r="C19" s="554" t="inlineStr">
+      <c r="C19" s="613" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="550">
+    <row r="20" ht="15" customHeight="1" s="614">
       <c r="A20" s="97" t="inlineStr">
         <is>
           <t>Área cubierta / cuarto de máquinas / tanques</t>
         </is>
       </c>
       <c r="B20" s="98" t="n"/>
-      <c r="C20" s="549" t="inlineStr">
+      <c r="C20" s="618" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="550">
+    <row r="21" ht="15" customHeight="1" s="614">
       <c r="A21" s="99" t="inlineStr">
         <is>
           <t>ÁREA TOTAL CONSTRUIDA</t>
@@ -10955,257 +10471,257 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="554" t="inlineStr">
+      <c r="C21" s="613" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="550">
+    <row r="22" ht="15" customHeight="1" s="614">
       <c r="A22" s="97" t="inlineStr">
         <is>
           <t>Número de apartamentos</t>
         </is>
       </c>
       <c r="B22" s="98" t="n"/>
-      <c r="C22" s="549" t="inlineStr">
+      <c r="C22" s="618" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="550">
+    <row r="23" ht="15" customHeight="1" s="614">
       <c r="A23" s="99" t="inlineStr">
         <is>
           <t>Área promedio por apartamento (vendible)</t>
         </is>
       </c>
       <c r="B23" s="100" t="n"/>
-      <c r="C23" s="554" t="inlineStr">
+      <c r="C23" s="613" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="550">
+    <row r="24" ht="15" customHeight="1" s="614">
       <c r="A24" s="97" t="inlineStr">
         <is>
           <t>Número de parqueaderos</t>
         </is>
       </c>
       <c r="B24" s="98" t="n"/>
-      <c r="C24" s="549" t="inlineStr">
+      <c r="C24" s="618" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="550">
+    <row r="25" ht="15" customHeight="1" s="614">
       <c r="A25" s="99" t="inlineStr">
         <is>
           <t>Número de ascensores</t>
         </is>
       </c>
       <c r="B25" s="100" t="n"/>
-      <c r="C25" s="554" t="inlineStr">
+      <c r="C25" s="613" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="550">
+    <row r="26" ht="15" customHeight="1" s="614">
       <c r="A26" s="97" t="inlineStr">
         <is>
           <t>Altura total aproximada (sótano a cubierta)</t>
         </is>
       </c>
       <c r="B26" s="98" t="n"/>
-      <c r="C26" s="549" t="inlineStr">
+      <c r="C26" s="618" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="555" t="n"/>
-      <c r="B27" s="555" t="n"/>
-      <c r="C27" s="555" t="n"/>
+      <c r="A27" s="617" t="n"/>
+      <c r="B27" s="617" t="n"/>
+      <c r="C27" s="617" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="550">
-      <c r="A28" s="553" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="614">
+      <c r="A28" s="616" t="inlineStr">
         <is>
           <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="550">
+    <row r="29" ht="15" customHeight="1" s="614">
       <c r="A29" s="97" t="inlineStr">
         <is>
           <t>Administración (A)</t>
         </is>
       </c>
-      <c r="B29" s="1283" t="n">
+      <c r="B29" s="1381" t="n">
         <v>0.1</v>
       </c>
-      <c r="C29" s="549" t="inlineStr">
+      <c r="C29" s="618" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="550">
+    <row r="30" ht="15" customHeight="1" s="614">
       <c r="A30" s="99" t="inlineStr">
         <is>
           <t>Imprevistos (I)</t>
         </is>
       </c>
-      <c r="B30" s="1284" t="n">
+      <c r="B30" s="1382" t="n">
         <v>0.04</v>
       </c>
-      <c r="C30" s="554" t="inlineStr">
+      <c r="C30" s="613" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="550">
+    <row r="31" ht="15" customHeight="1" s="614">
       <c r="A31" s="97" t="inlineStr">
         <is>
           <t>Utilidad (U)</t>
         </is>
       </c>
-      <c r="B31" s="1283" t="n">
+      <c r="B31" s="1381" t="n">
         <v>0.12</v>
       </c>
-      <c r="C31" s="549" t="inlineStr">
+      <c r="C31" s="618" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="550">
+    <row r="32" ht="15" customHeight="1" s="614">
       <c r="A32" s="99" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="B32" s="1284" t="n">
+      <c r="B32" s="1382" t="n">
         <v>0.19</v>
       </c>
-      <c r="C32" s="554" t="inlineStr">
+      <c r="C32" s="613" t="inlineStr">
         <is>
           <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="555" t="n"/>
-      <c r="B33" s="555" t="n"/>
-      <c r="C33" s="555" t="n"/>
+      <c r="A33" s="617" t="n"/>
+      <c r="B33" s="617" t="n"/>
+      <c r="C33" s="617" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="550">
+    <row r="34" ht="15" customHeight="1" s="614">
       <c r="A34" s="103" t="inlineStr">
         <is>
           <t>AIU TOTAL (A+I+U)</t>
         </is>
       </c>
-      <c r="B34" s="1285">
+      <c r="B34" s="1383">
         <f>B29+B30+B31</f>
         <v/>
       </c>
-      <c r="C34" s="555" t="n"/>
+      <c r="C34" s="617" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="555" t="n"/>
-      <c r="B35" s="555" t="n"/>
-      <c r="C35" s="555" t="n"/>
+      <c r="A35" s="617" t="n"/>
+      <c r="B35" s="617" t="n"/>
+      <c r="C35" s="617" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="550">
-      <c r="A36" s="553" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="614">
+      <c r="A36" s="616" t="inlineStr">
         <is>
           <t>FUENTES Y NOTAS METODOLÓGICAS</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customFormat="1" customHeight="1" s="199">
-      <c r="A37" s="200" t="inlineStr">
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="198">
+      <c r="A37" s="199" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B37" s="198" t="n"/>
-      <c r="C37" s="198" t="n"/>
-      <c r="D37" s="198" t="n"/>
-      <c r="E37" s="337">
+      <c r="B37" s="197" t="n"/>
+      <c r="C37" s="197" t="n"/>
+      <c r="D37" s="197" t="n"/>
+      <c r="E37" s="332">
         <f>E4</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="25.5" customHeight="1" s="550">
-      <c r="A38" s="551" t="inlineStr">
+    <row r="38" ht="25.5" customHeight="1" s="614">
+      <c r="A38" s="615" t="inlineStr">
         <is>
           <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="25.5" customHeight="1" s="550">
-      <c r="A39" s="551" t="inlineStr">
+    <row r="39" ht="25.5" customHeight="1" s="614">
+      <c r="A39" s="615" t="inlineStr">
         <is>
           <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="25.5" customHeight="1" s="550">
-      <c r="A40" s="551" t="inlineStr">
+    <row r="40" ht="25.5" customHeight="1" s="614">
+      <c r="A40" s="615" t="inlineStr">
         <is>
           <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="25.5" customHeight="1" s="550">
-      <c r="A41" s="551" t="inlineStr">
+    <row r="41" ht="25.5" customHeight="1" s="614">
+      <c r="A41" s="615" t="inlineStr">
         <is>
           <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="25.5" customHeight="1" s="550">
-      <c r="A42" s="551" t="inlineStr">
+    <row r="42" ht="25.5" customHeight="1" s="614">
+      <c r="A42" s="615" t="inlineStr">
         <is>
           <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="25.5" customHeight="1" s="550">
-      <c r="A43" s="551" t="inlineStr">
+    <row r="43" ht="25.5" customHeight="1" s="614">
+      <c r="A43" s="615" t="inlineStr">
         <is>
           <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="25.5" customHeight="1" s="550">
-      <c r="A44" s="551" t="inlineStr">
+    <row r="44" ht="25.5" customHeight="1" s="614">
+      <c r="A44" s="615" t="inlineStr">
         <is>
           <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="25.5" customHeight="1" s="550">
-      <c r="A45" s="551" t="inlineStr">
+    <row r="45" ht="25.5" customHeight="1" s="614">
+      <c r="A45" s="615" t="inlineStr">
         <is>
           <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="25.5" customHeight="1" s="550">
-      <c r="A46" s="551" t="inlineStr">
+    <row r="46" ht="25.5" customHeight="1" s="614">
+      <c r="A46" s="615" t="inlineStr">
         <is>
           <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="25.5" customHeight="1" s="550">
-      <c r="A47" s="551" t="inlineStr">
+    <row r="47" ht="25.5" customHeight="1" s="614">
+      <c r="A47" s="615" t="inlineStr">
         <is>
           <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
         </is>
@@ -11241,19 +10757,19 @@
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
